--- a/submissions/henkvaness_track2_methods.xlsx
+++ b/submissions/henkvaness_track2_methods.xlsx
@@ -677,7 +677,6 @@
     </row>
     <row r="3"/>
     <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="16" customHeight="1" s="7">
       <c r="B6" s="1" t="inlineStr">
         <is>
@@ -717,7 +716,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Anthropic, Claude Code on a Max plan, model-improvement sharing disabled, no output rating. Used to run the panels, the literature and database work, the computation and the drafting. No patient data was sent to any third-party service; all variant-level processing was local, and public resources were read as static files rather than queried.</t>
+          <t>Three providers were used and all three are named here. (1) Anthropic, Claude Code on a Max plan, model-improvement sharing disabled, no output rating: this did the panels, the literature and database work, the computation and the drafting. (2) OpenAI API, GPT-5, and (3) Google Vertex AI, Gemini 3.1 Pro run on the author's own server: four neutral prompts each, used only as cross-checks on the project's own documents, contributing no content; their outputs are in vertex/out/. The Anthropic API, separately from Claude Code, was also used for one external read of the project's own derived files. What was and was not transmitted: the whole-genome VCF was never sent to any model and the raw reads were never downloaded. What was sent to providers (2) and (3), and to the Anthropic API, is a de-identified corpus of this project's own documents, with variant coordinates, protein changes, sample and proband identifiers, HPO identifiers and named clinical features replaced with stable tokens before transmission, 331 substitutions across 68 files, leak-checked afterwards; the substitution mapping was kept local. All variant-level processing was local, and public resources were read as static files or by byte range rather than queried with patient coordinates. Full detail in track2/anomalies/COMPLIANCE.md.</t>
         </is>
       </c>
     </row>
